--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,370 +394,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>61</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>45</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>34</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>17</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>21</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>31</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>45</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>42</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>45</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>52</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>61</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>63</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>52</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>47</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>45</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>37</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>11</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B47">
-        <v>26</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,282 +394,322 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>1076</v>
+        <v>850</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>1083</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>1110</v>
+        <v>761</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>1220</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>1349</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>1490</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>1574</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>1587</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>1572</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>1615</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>1635</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>1625</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>1579</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>1534</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>1501</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>1516</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>1533</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>1551</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>1523</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>1443</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>1411</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>1429</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>1414</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>1465</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>1487</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>1511</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>1554</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>1580</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>1571</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>1562</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>1564</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>1621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>1579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>1554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>1556</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46283.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46283.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B41">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,322 +394,266 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>850</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>799</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>761</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>690</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>636</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>592</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>556</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>536</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>516</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>473</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>435</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>399</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>361</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>325</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>295</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>259</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>167</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>150</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>103</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="2">
-        <v>46283.34375</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2">
-        <v>46283.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46283.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46283.375</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46283.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46283.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46283.40625</v>
-      </c>
-      <c r="B41">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,266 +394,314 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
-        <v>26</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
-        <v>69</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
-        <v>86</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
-        <v>102</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
-        <v>130</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
-        <v>118</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
-        <v>110</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
-        <v>107</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
-        <v>122</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
-        <v>119</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
-        <v>102</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
-        <v>87</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
-        <v>72</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>60</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>50</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>41</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>29</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>21</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>18</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
+        <v>46295.34375</v>
+      </c>
+      <c r="B35">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46295.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46295.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46295.375</v>
+      </c>
+      <c r="B38">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46295.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -26,9 +26,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -81,12 +78,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -392,318 +388,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2">
-        <v>46295</v>
-      </c>
-      <c r="B2">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2">
-        <v>46295.01041666666</v>
-      </c>
-      <c r="B3">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2">
-        <v>46295.02083333334</v>
-      </c>
-      <c r="B4">
-        <v>2321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2">
-        <v>46295.03125</v>
-      </c>
-      <c r="B5">
-        <v>2285</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2">
-        <v>46295.04166666666</v>
-      </c>
-      <c r="B6">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2">
-        <v>46295.05208333334</v>
-      </c>
-      <c r="B7">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2">
-        <v>46295.0625</v>
-      </c>
-      <c r="B8">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2">
-        <v>46295.07291666666</v>
-      </c>
-      <c r="B9">
-        <v>2102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>46295.08333333334</v>
-      </c>
-      <c r="B10">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>46295.09375</v>
-      </c>
-      <c r="B11">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>46295.10416666666</v>
-      </c>
-      <c r="B12">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>46295.11458333334</v>
-      </c>
-      <c r="B13">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>46295.125</v>
-      </c>
-      <c r="B14">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2">
-        <v>46295.13541666666</v>
-      </c>
-      <c r="B15">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2">
-        <v>46295.14583333334</v>
-      </c>
-      <c r="B16">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2">
-        <v>46295.15625</v>
-      </c>
-      <c r="B17">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2">
-        <v>46295.16666666666</v>
-      </c>
-      <c r="B18">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2">
-        <v>46295.17708333334</v>
-      </c>
-      <c r="B19">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2">
-        <v>46295.1875</v>
-      </c>
-      <c r="B20">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2">
-        <v>46295.19791666666</v>
-      </c>
-      <c r="B21">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2">
-        <v>46295.20833333334</v>
-      </c>
-      <c r="B22">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2">
-        <v>46295.21875</v>
-      </c>
-      <c r="B23">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2">
-        <v>46295.22916666666</v>
-      </c>
-      <c r="B24">
-        <v>1824</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2">
-        <v>46295.23958333334</v>
-      </c>
-      <c r="B25">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2">
-        <v>46295.25</v>
-      </c>
-      <c r="B26">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="2">
-        <v>46295.26041666666</v>
-      </c>
-      <c r="B27">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="2">
-        <v>46295.27083333334</v>
-      </c>
-      <c r="B28">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="2">
-        <v>46295.28125</v>
-      </c>
-      <c r="B29">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="2">
-        <v>46295.29166666666</v>
-      </c>
-      <c r="B30">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="2">
-        <v>46295.30208333334</v>
-      </c>
-      <c r="B31">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="2">
-        <v>46295.3125</v>
-      </c>
-      <c r="B32">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="2">
-        <v>46295.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="2">
-        <v>46295.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="2">
-        <v>46295.34375</v>
-      </c>
-      <c r="B35">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2">
-        <v>46295.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46295.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46295.375</v>
-      </c>
-      <c r="B38">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46295.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46295.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>1232</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -26,6 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -78,11 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +392,3398 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>46298.01041666666</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>46298.02083333334</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>46298.03125</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>46298.04166666666</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>46298.05208333334</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>46298.0625</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>46298.07291666666</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>46298.08333333334</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>46298.09375</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>46298.10416666666</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>46298.11458333334</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>46298.125</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>46298.13541666666</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>46298.14583333334</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>46298.15625</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>46298.16666666666</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>46298.17708333334</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>46298.1875</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>46298.19791666666</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>46298.20833333334</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>46298.21875</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>46298.22916666666</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>46298.23958333334</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>46298.25</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>46298.26041666666</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2">
+        <v>46298.27083333334</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2">
+        <v>46298.28125</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2">
+        <v>46298.29166666666</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2">
+        <v>46298.30208333334</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2">
+        <v>46298.3125</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2">
+        <v>46298.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2">
+        <v>46298.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
+        <v>46298.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46298.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46298.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46298.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46298.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46298.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46298.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46298.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46298.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46298.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46298.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46298.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46298.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46298.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46298.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46298.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46298.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46298.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46298.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46298.5625</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
+        <v>46298.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
+        <v>46298.59375</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
+        <v>46298.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2">
+        <v>46298.61458333334</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2">
+        <v>46298.625</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2">
+        <v>46298.63541666666</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2">
+        <v>46298.64583333334</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2">
+        <v>46298.65625</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
+        <v>46298.67708333334</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
+        <v>46298.6875</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
+        <v>46298.69791666666</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2">
+        <v>46298.71875</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2">
+        <v>46298.72916666666</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2">
+        <v>46298.73958333334</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2">
+        <v>46298.75</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2">
+        <v>46298.76041666666</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
+        <v>46298.77083333334</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2">
+        <v>46298.78125</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2">
+        <v>46298.79166666666</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2">
+        <v>46298.80208333334</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2">
+        <v>46298.8125</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46298.82291666666</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
+        <v>46298.83333333334</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
+        <v>46298.84375</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>46298.85416666666</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
+        <v>46298.86458333334</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2">
+        <v>46298.875</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2">
+        <v>46298.88541666666</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2">
+        <v>46298.89583333334</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
+        <v>46298.90625</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
+        <v>46298.91666666666</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
+        <v>46298.92708333334</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46298.9375</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46298.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46298.96875</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46298.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46299.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46299.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46299.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46299.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46299.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46299.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46299.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46299.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46299.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46299.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46299.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46299.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46299.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46299.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46299.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46299.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46299.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46299.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46299.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46299.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46299.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46299.25</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46299.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46299.28125</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46299.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46299.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46299.3125</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46299.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46299.34375</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46299.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1058 +394,1050 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>191</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>172</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>163</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>151</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>128</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>114</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>101</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>89</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>88</v>
+        <v>947</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>81</v>
+        <v>923</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>69</v>
+        <v>884</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>60</v>
+        <v>858</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>50</v>
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>40</v>
+        <v>804</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>816</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>26</v>
+        <v>824</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>821</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>820</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>8</v>
+        <v>781</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>749</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>742</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>776</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>803</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>845</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>850</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>845</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>867</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>874</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>866</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>778</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>648</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>691</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>694</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>712</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>713</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>14</v>
+        <v>733</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>20</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>31</v>
+        <v>818</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>46</v>
+        <v>854</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>53</v>
+        <v>897</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>62</v>
+        <v>936</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>57</v>
+        <v>982</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>54</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>61</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>69</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>75</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>87</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>89</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>107</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>121</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>142</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>202</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>281</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>346</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>409</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>475</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>549</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>578</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>624</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>670</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>710</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>725</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>720</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>724</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>738</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>802</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>876</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>948</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>1003</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>1048</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>1088</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>1128</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>1158</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>1160</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>1152</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>1157</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>1177</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>1225</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1249</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1267</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>1285</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>1281</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>1285</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>1271</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>1258</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1251</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>1259</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>1268</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>1254</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1209</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1187</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>1169</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>1157</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1130</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1101</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>1096</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>1075</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>1045</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>1009</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>947</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>923</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>909</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>884</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>858</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>822</v>
+        <v>973</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>804</v>
+        <v>949</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>816</v>
+        <v>935</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>824</v>
+        <v>903</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>821</v>
+        <v>883</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>820</v>
+        <v>861</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>781</v>
+        <v>809</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>749</v>
+        <v>762</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>748</v>
+        <v>724</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>760</v>
+        <v>713</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>776</v>
+        <v>718</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>803</v>
+        <v>719</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>845</v>
+        <v>708</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>850</v>
+        <v>704</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>845</v>
+        <v>708</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>867</v>
+        <v>701</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>874</v>
+        <v>661</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>866</v>
+        <v>586</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>778</v>
+        <v>510</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>681</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46303.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>673</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,314 +394,442 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>758</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>726</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>726</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>728</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>712</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>737</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>731</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>727</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>708</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>712</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>727</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>728</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>768</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>883</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>1053</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>1216</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>1241</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>1139</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>1188</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>1191</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>1416</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>1507</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>1462</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>1377</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>1241</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>1102</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>1014</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>888</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>775</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>662</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>598</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>568</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>558</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>560</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>567</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>580</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>602</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>639</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>661</v>
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46308.40625</v>
+      </c>
+      <c r="B41">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46308.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46308.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46308.4375</v>
+      </c>
+      <c r="B44">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46308.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46308.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46308.46875</v>
+      </c>
+      <c r="B47">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46308.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46308.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46308.5</v>
+      </c>
+      <c r="B50">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46308.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46308.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46308.53125</v>
+      </c>
+      <c r="B53">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46308.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46308.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46308.5625</v>
+      </c>
+      <c r="B56">
+        <v>2739</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,442 +394,474 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
-        <v>2259</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
-        <v>2236</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
-        <v>2206</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
-        <v>2171</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
-        <v>2133</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
-        <v>2153</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
-        <v>2170</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
-        <v>2161</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
-        <v>2161</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
-        <v>2173</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
-        <v>2153</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
-        <v>2112</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
-        <v>2118</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
-        <v>2095</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
-        <v>2110</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
-        <v>2145</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
-        <v>2141</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
-        <v>2150</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
-        <v>2126</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
-        <v>2139</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
-        <v>2201</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
-        <v>2305</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
-        <v>2397</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
-        <v>2433</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
-        <v>2466</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
-        <v>2442</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
-        <v>2426</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>2464</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>2522</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>2573</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
-        <v>2597</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
-        <v>2609</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
-        <v>2601</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
-        <v>2627</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
-        <v>2662</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>2656</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>2650</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>2648</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>2672</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>2667</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>2684</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>2679</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>2672</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>2651</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>2668</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
-        <v>2687</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
-        <v>2701</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
-        <v>2704</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>2678</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>2667</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>2686</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>2699</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>2788</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>2779</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>2739</v>
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B59">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>2208</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,474 +394,410 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>2228</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>2256</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>2299</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>2333</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>2306</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>2239</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>2238</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>2281</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>2303</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>2331</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>2400</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
-        <v>2440</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>2443</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>2434</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>2445</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>2433</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>2400</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>2375</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>2404</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>2456</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>2440</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>2420</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>2440</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>2428</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>2377</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>2364</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>2355</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>2318</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>2271</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>2277</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>2353</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>2430</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>2481</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>2480</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>2481</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>2467</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>2424</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>2355</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>2318</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>2269</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>2210</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>2249</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>2233</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>2209</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>2203</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>2187</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>2224</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>2228</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>2281</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>2341</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>2386</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2">
-        <v>46309.53125</v>
-      </c>
-      <c r="B53">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>2534</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B56">
-        <v>2539</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B58">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B59">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="2">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="B60">
-        <v>2208</v>
+        <v>1705</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,410 +394,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>1722</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>1633</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>1563</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>1642</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>1670</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>1678</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
-        <v>1718</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>1750</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>1721</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
-        <v>1645</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>1604</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
-        <v>1574</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>1518</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>1483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>1504</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>1553</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>1551</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>1521</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
-        <v>1496</v>
+        <v>646</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
-        <v>1564</v>
+        <v>682</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
-        <v>1596</v>
+        <v>698</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
-        <v>1562</v>
+        <v>662</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>1606</v>
+        <v>707</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>1643</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>1657</v>
+        <v>804</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>1684</v>
+        <v>812</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>1662</v>
+        <v>814</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>1663</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>1639</v>
+        <v>851</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>1616</v>
+        <v>847</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>1538</v>
+        <v>864</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>1486</v>
+        <v>834</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>1503</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>1515</v>
+        <v>763</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>1558</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B38">
-        <v>1804</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B41">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B44">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B47">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B50">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>1705</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,282 +394,306 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
-        <v>551</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
-        <v>554</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
-        <v>542</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
-        <v>533</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
-        <v>546</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
-        <v>574</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
-        <v>594</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
-        <v>574</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
-        <v>537</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
-        <v>523</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
-        <v>505</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
-        <v>490</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
-        <v>493</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
-        <v>485</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
-        <v>476</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
-        <v>482</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
-        <v>509</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
-        <v>583</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
-        <v>646</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
-        <v>682</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
-        <v>698</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
-        <v>662</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
-        <v>707</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
-        <v>762</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
-        <v>804</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
-        <v>812</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
-        <v>814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
-        <v>839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>847</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>864</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>834</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>798</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>763</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>705</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46320.32291666666</v>
+      </c>
+      <c r="B37">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="B38">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46320.34375</v>
+      </c>
+      <c r="B39">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
